--- a/data_execl/base_data/AfkSpeak.xlsx
+++ b/data_execl/base_data/AfkSpeak.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C440E5-A6AF-463E-9A29-F8D6B97E2DA5}">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -1663,6 +1663,446 @@
       </c>
       <c r="D113">
         <v>63010108</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B114">
+        <v>107</v>
+      </c>
+      <c r="C114">
+        <v>9901</v>
+      </c>
+      <c r="D114">
+        <v>63010109</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B115">
+        <v>108</v>
+      </c>
+      <c r="C115">
+        <v>9901</v>
+      </c>
+      <c r="D115">
+        <v>63010110</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B116">
+        <v>109</v>
+      </c>
+      <c r="C116">
+        <v>9901</v>
+      </c>
+      <c r="D116">
+        <v>63010111</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B117">
+        <v>110</v>
+      </c>
+      <c r="C117">
+        <v>9901</v>
+      </c>
+      <c r="D117">
+        <v>63010112</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B118">
+        <v>111</v>
+      </c>
+      <c r="C118">
+        <v>9901</v>
+      </c>
+      <c r="D118">
+        <v>63010113</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B119">
+        <v>112</v>
+      </c>
+      <c r="C119">
+        <v>9901</v>
+      </c>
+      <c r="D119">
+        <v>63010114</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B120">
+        <v>113</v>
+      </c>
+      <c r="C120">
+        <v>9901</v>
+      </c>
+      <c r="D120">
+        <v>63010115</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B121">
+        <v>114</v>
+      </c>
+      <c r="C121">
+        <v>9901</v>
+      </c>
+      <c r="D121">
+        <v>63010116</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B122">
+        <v>115</v>
+      </c>
+      <c r="C122">
+        <v>9902</v>
+      </c>
+      <c r="D122">
+        <v>63010117</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B123">
+        <v>116</v>
+      </c>
+      <c r="C123">
+        <v>9902</v>
+      </c>
+      <c r="D123">
+        <v>63010118</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B124">
+        <v>117</v>
+      </c>
+      <c r="C124">
+        <v>9902</v>
+      </c>
+      <c r="D124">
+        <v>63010119</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B125">
+        <v>118</v>
+      </c>
+      <c r="C125">
+        <v>9902</v>
+      </c>
+      <c r="D125">
+        <v>63010120</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B126">
+        <v>119</v>
+      </c>
+      <c r="C126">
+        <v>9902</v>
+      </c>
+      <c r="D126">
+        <v>63010121</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B127">
+        <v>120</v>
+      </c>
+      <c r="C127">
+        <v>9902</v>
+      </c>
+      <c r="D127">
+        <v>63010122</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B128">
+        <v>121</v>
+      </c>
+      <c r="C128">
+        <v>9902</v>
+      </c>
+      <c r="D128">
+        <v>63010123</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B129">
+        <v>122</v>
+      </c>
+      <c r="C129">
+        <v>9902</v>
+      </c>
+      <c r="D129">
+        <v>63010124</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B130">
+        <v>123</v>
+      </c>
+      <c r="C130">
+        <v>9905</v>
+      </c>
+      <c r="D130">
+        <v>63010125</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B131">
+        <v>124</v>
+      </c>
+      <c r="C131">
+        <v>9905</v>
+      </c>
+      <c r="D131">
+        <v>63010126</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B132">
+        <v>125</v>
+      </c>
+      <c r="C132">
+        <v>9905</v>
+      </c>
+      <c r="D132">
+        <v>63010127</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B133">
+        <v>126</v>
+      </c>
+      <c r="C133">
+        <v>9905</v>
+      </c>
+      <c r="D133">
+        <v>63010128</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B134">
+        <v>127</v>
+      </c>
+      <c r="C134">
+        <v>9905</v>
+      </c>
+      <c r="D134">
+        <v>63010129</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B135">
+        <v>128</v>
+      </c>
+      <c r="C135">
+        <v>9905</v>
+      </c>
+      <c r="D135">
+        <v>63010130</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B136">
+        <v>129</v>
+      </c>
+      <c r="C136">
+        <v>9905</v>
+      </c>
+      <c r="D136">
+        <v>63010131</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B137">
+        <v>130</v>
+      </c>
+      <c r="C137">
+        <v>9905</v>
+      </c>
+      <c r="D137">
+        <v>63010132</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B138">
+        <v>131</v>
+      </c>
+      <c r="C138">
+        <v>9907</v>
+      </c>
+      <c r="D138">
+        <v>63010133</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B139">
+        <v>132</v>
+      </c>
+      <c r="C139">
+        <v>9907</v>
+      </c>
+      <c r="D139">
+        <v>63010134</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B140">
+        <v>133</v>
+      </c>
+      <c r="C140">
+        <v>9907</v>
+      </c>
+      <c r="D140">
+        <v>63010135</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B141">
+        <v>134</v>
+      </c>
+      <c r="C141">
+        <v>9907</v>
+      </c>
+      <c r="D141">
+        <v>63010136</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B142">
+        <v>135</v>
+      </c>
+      <c r="C142">
+        <v>9907</v>
+      </c>
+      <c r="D142">
+        <v>63010137</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B143">
+        <v>136</v>
+      </c>
+      <c r="C143">
+        <v>9907</v>
+      </c>
+      <c r="D143">
+        <v>63010138</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B144">
+        <v>137</v>
+      </c>
+      <c r="C144">
+        <v>9907</v>
+      </c>
+      <c r="D144">
+        <v>63010139</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B145">
+        <v>138</v>
+      </c>
+      <c r="C145">
+        <v>9907</v>
+      </c>
+      <c r="D145">
+        <v>63010140</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B146">
+        <v>139</v>
+      </c>
+      <c r="C146">
+        <v>9908</v>
+      </c>
+      <c r="D146">
+        <v>63010141</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B147">
+        <v>140</v>
+      </c>
+      <c r="C147">
+        <v>9908</v>
+      </c>
+      <c r="D147">
+        <v>63010142</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B148">
+        <v>141</v>
+      </c>
+      <c r="C148">
+        <v>9908</v>
+      </c>
+      <c r="D148">
+        <v>63010143</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B149">
+        <v>142</v>
+      </c>
+      <c r="C149">
+        <v>9908</v>
+      </c>
+      <c r="D149">
+        <v>63010144</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B150">
+        <v>143</v>
+      </c>
+      <c r="C150">
+        <v>9908</v>
+      </c>
+      <c r="D150">
+        <v>63010145</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B151">
+        <v>144</v>
+      </c>
+      <c r="C151">
+        <v>9908</v>
+      </c>
+      <c r="D151">
+        <v>63010146</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B152">
+        <v>145</v>
+      </c>
+      <c r="C152">
+        <v>9908</v>
+      </c>
+      <c r="D152">
+        <v>63010147</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B153">
+        <v>146</v>
+      </c>
+      <c r="C153">
+        <v>9908</v>
+      </c>
+      <c r="D153">
+        <v>63010148</v>
       </c>
     </row>
   </sheetData>

--- a/data_execl/base_data/AfkSpeak.xlsx
+++ b/data_execl/base_data/AfkSpeak.xlsx
@@ -431,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C440E5-A6AF-463E-9A29-F8D6B97E2DA5}">
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -2105,6 +2105,1194 @@
         <v>63010148</v>
       </c>
     </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B154">
+        <v>147</v>
+      </c>
+      <c r="C154">
+        <v>50005</v>
+      </c>
+      <c r="D154">
+        <v>63010149</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B155">
+        <v>148</v>
+      </c>
+      <c r="C155">
+        <v>50005</v>
+      </c>
+      <c r="D155">
+        <v>63010150</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B156">
+        <v>149</v>
+      </c>
+      <c r="C156">
+        <v>50007</v>
+      </c>
+      <c r="D156">
+        <v>63010151</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B157">
+        <v>150</v>
+      </c>
+      <c r="C157">
+        <v>50007</v>
+      </c>
+      <c r="D157">
+        <v>63010152</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B158">
+        <v>151</v>
+      </c>
+      <c r="C158">
+        <v>50008</v>
+      </c>
+      <c r="D158">
+        <v>63010153</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B159">
+        <v>152</v>
+      </c>
+      <c r="C159">
+        <v>50008</v>
+      </c>
+      <c r="D159">
+        <v>63010154</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B160">
+        <v>153</v>
+      </c>
+      <c r="C160">
+        <v>50009</v>
+      </c>
+      <c r="D160">
+        <v>63010155</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B161">
+        <v>154</v>
+      </c>
+      <c r="C161">
+        <v>50009</v>
+      </c>
+      <c r="D161">
+        <v>63010156</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B162">
+        <v>155</v>
+      </c>
+      <c r="C162">
+        <v>50010</v>
+      </c>
+      <c r="D162">
+        <v>63010157</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B163">
+        <v>156</v>
+      </c>
+      <c r="C163">
+        <v>50010</v>
+      </c>
+      <c r="D163">
+        <v>63010158</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B164">
+        <v>157</v>
+      </c>
+      <c r="C164">
+        <v>50011</v>
+      </c>
+      <c r="D164">
+        <v>63010159</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B165">
+        <v>158</v>
+      </c>
+      <c r="C165">
+        <v>50011</v>
+      </c>
+      <c r="D165">
+        <v>63010160</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B166">
+        <v>159</v>
+      </c>
+      <c r="C166">
+        <v>50012</v>
+      </c>
+      <c r="D166">
+        <v>63010161</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B167">
+        <v>160</v>
+      </c>
+      <c r="C167">
+        <v>50012</v>
+      </c>
+      <c r="D167">
+        <v>63010162</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B168">
+        <v>161</v>
+      </c>
+      <c r="C168">
+        <v>50013</v>
+      </c>
+      <c r="D168">
+        <v>63010163</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B169">
+        <v>162</v>
+      </c>
+      <c r="C169">
+        <v>50013</v>
+      </c>
+      <c r="D169">
+        <v>63010164</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B170">
+        <v>163</v>
+      </c>
+      <c r="C170">
+        <v>50014</v>
+      </c>
+      <c r="D170">
+        <v>63010165</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B171">
+        <v>164</v>
+      </c>
+      <c r="C171">
+        <v>50014</v>
+      </c>
+      <c r="D171">
+        <v>63010166</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B172">
+        <v>165</v>
+      </c>
+      <c r="C172">
+        <v>50015</v>
+      </c>
+      <c r="D172">
+        <v>63010167</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B173">
+        <v>166</v>
+      </c>
+      <c r="C173">
+        <v>50015</v>
+      </c>
+      <c r="D173">
+        <v>63010168</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B174">
+        <v>167</v>
+      </c>
+      <c r="C174">
+        <v>50016</v>
+      </c>
+      <c r="D174">
+        <v>63010169</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B175">
+        <v>168</v>
+      </c>
+      <c r="C175">
+        <v>50016</v>
+      </c>
+      <c r="D175">
+        <v>63010170</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B176">
+        <v>169</v>
+      </c>
+      <c r="C176">
+        <v>50017</v>
+      </c>
+      <c r="D176">
+        <v>63010171</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B177">
+        <v>170</v>
+      </c>
+      <c r="C177">
+        <v>50017</v>
+      </c>
+      <c r="D177">
+        <v>63010172</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B178">
+        <v>171</v>
+      </c>
+      <c r="C178">
+        <v>50018</v>
+      </c>
+      <c r="D178">
+        <v>63010173</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B179">
+        <v>172</v>
+      </c>
+      <c r="C179">
+        <v>50018</v>
+      </c>
+      <c r="D179">
+        <v>63010174</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B180">
+        <v>173</v>
+      </c>
+      <c r="C180">
+        <v>50019</v>
+      </c>
+      <c r="D180">
+        <v>63010175</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B181">
+        <v>174</v>
+      </c>
+      <c r="C181">
+        <v>50019</v>
+      </c>
+      <c r="D181">
+        <v>63010176</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B182">
+        <v>175</v>
+      </c>
+      <c r="C182">
+        <v>50022</v>
+      </c>
+      <c r="D182">
+        <v>63010177</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B183">
+        <v>176</v>
+      </c>
+      <c r="C183">
+        <v>50022</v>
+      </c>
+      <c r="D183">
+        <v>63010178</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B184">
+        <v>177</v>
+      </c>
+      <c r="C184">
+        <v>50023</v>
+      </c>
+      <c r="D184">
+        <v>63010179</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B185">
+        <v>178</v>
+      </c>
+      <c r="C185">
+        <v>50023</v>
+      </c>
+      <c r="D185">
+        <v>63010180</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B186">
+        <v>179</v>
+      </c>
+      <c r="C186">
+        <v>50027</v>
+      </c>
+      <c r="D186">
+        <v>63010181</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B187">
+        <v>180</v>
+      </c>
+      <c r="C187">
+        <v>50027</v>
+      </c>
+      <c r="D187">
+        <v>63010182</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B188">
+        <v>181</v>
+      </c>
+      <c r="C188">
+        <v>50029</v>
+      </c>
+      <c r="D188">
+        <v>63010183</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B189">
+        <v>182</v>
+      </c>
+      <c r="C189">
+        <v>50029</v>
+      </c>
+      <c r="D189">
+        <v>63010184</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B190">
+        <v>183</v>
+      </c>
+      <c r="C190">
+        <v>50030</v>
+      </c>
+      <c r="D190">
+        <v>63010185</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B191">
+        <v>184</v>
+      </c>
+      <c r="C191">
+        <v>50030</v>
+      </c>
+      <c r="D191">
+        <v>63010186</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B192">
+        <v>185</v>
+      </c>
+      <c r="C192">
+        <v>50031</v>
+      </c>
+      <c r="D192">
+        <v>63010187</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B193">
+        <v>186</v>
+      </c>
+      <c r="C193">
+        <v>50031</v>
+      </c>
+      <c r="D193">
+        <v>63010188</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B194">
+        <v>187</v>
+      </c>
+      <c r="C194">
+        <v>50032</v>
+      </c>
+      <c r="D194">
+        <v>63010189</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B195">
+        <v>188</v>
+      </c>
+      <c r="C195">
+        <v>50032</v>
+      </c>
+      <c r="D195">
+        <v>63010190</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B196">
+        <v>189</v>
+      </c>
+      <c r="C196">
+        <v>50033</v>
+      </c>
+      <c r="D196">
+        <v>63010191</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B197">
+        <v>190</v>
+      </c>
+      <c r="C197">
+        <v>50033</v>
+      </c>
+      <c r="D197">
+        <v>63010192</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B198">
+        <v>191</v>
+      </c>
+      <c r="C198">
+        <v>50034</v>
+      </c>
+      <c r="D198">
+        <v>63010193</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B199">
+        <v>192</v>
+      </c>
+      <c r="C199">
+        <v>50034</v>
+      </c>
+      <c r="D199">
+        <v>63010194</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B200">
+        <v>193</v>
+      </c>
+      <c r="C200">
+        <v>50035</v>
+      </c>
+      <c r="D200">
+        <v>63010195</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B201">
+        <v>194</v>
+      </c>
+      <c r="C201">
+        <v>50035</v>
+      </c>
+      <c r="D201">
+        <v>63010196</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B202">
+        <v>195</v>
+      </c>
+      <c r="C202">
+        <v>50038</v>
+      </c>
+      <c r="D202">
+        <v>63010197</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B203">
+        <v>196</v>
+      </c>
+      <c r="C203">
+        <v>50038</v>
+      </c>
+      <c r="D203">
+        <v>63010198</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B204">
+        <v>197</v>
+      </c>
+      <c r="C204">
+        <v>50039</v>
+      </c>
+      <c r="D204">
+        <v>63010199</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B205">
+        <v>198</v>
+      </c>
+      <c r="C205">
+        <v>50039</v>
+      </c>
+      <c r="D205">
+        <v>63010200</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B206">
+        <v>199</v>
+      </c>
+      <c r="C206">
+        <v>50040</v>
+      </c>
+      <c r="D206">
+        <v>63010201</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B207">
+        <v>200</v>
+      </c>
+      <c r="C207">
+        <v>50040</v>
+      </c>
+      <c r="D207">
+        <v>63010202</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B208">
+        <v>201</v>
+      </c>
+      <c r="C208">
+        <v>50041</v>
+      </c>
+      <c r="D208">
+        <v>63010203</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B209">
+        <v>202</v>
+      </c>
+      <c r="C209">
+        <v>50041</v>
+      </c>
+      <c r="D209">
+        <v>63010204</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B210">
+        <v>203</v>
+      </c>
+      <c r="C210">
+        <v>50043</v>
+      </c>
+      <c r="D210">
+        <v>63010205</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B211">
+        <v>204</v>
+      </c>
+      <c r="C211">
+        <v>50043</v>
+      </c>
+      <c r="D211">
+        <v>63010206</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B212">
+        <v>205</v>
+      </c>
+      <c r="C212">
+        <v>50044</v>
+      </c>
+      <c r="D212">
+        <v>63010207</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B213">
+        <v>206</v>
+      </c>
+      <c r="C213">
+        <v>50044</v>
+      </c>
+      <c r="D213">
+        <v>63010208</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B214">
+        <v>207</v>
+      </c>
+      <c r="C214">
+        <v>50047</v>
+      </c>
+      <c r="D214">
+        <v>63010209</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B215">
+        <v>208</v>
+      </c>
+      <c r="C215">
+        <v>50047</v>
+      </c>
+      <c r="D215">
+        <v>63010210</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B216">
+        <v>209</v>
+      </c>
+      <c r="C216">
+        <v>50048</v>
+      </c>
+      <c r="D216">
+        <v>63010211</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B217">
+        <v>210</v>
+      </c>
+      <c r="C217">
+        <v>50048</v>
+      </c>
+      <c r="D217">
+        <v>63010212</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B218">
+        <v>211</v>
+      </c>
+      <c r="C218">
+        <v>50049</v>
+      </c>
+      <c r="D218">
+        <v>63010213</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B219">
+        <v>212</v>
+      </c>
+      <c r="C219">
+        <v>50049</v>
+      </c>
+      <c r="D219">
+        <v>63010214</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B220">
+        <v>213</v>
+      </c>
+      <c r="C220">
+        <v>50050</v>
+      </c>
+      <c r="D220">
+        <v>63010215</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B221">
+        <v>214</v>
+      </c>
+      <c r="C221">
+        <v>50050</v>
+      </c>
+      <c r="D221">
+        <v>63010216</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B222">
+        <v>215</v>
+      </c>
+      <c r="C222">
+        <v>50051</v>
+      </c>
+      <c r="D222">
+        <v>63010217</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B223">
+        <v>216</v>
+      </c>
+      <c r="C223">
+        <v>50051</v>
+      </c>
+      <c r="D223">
+        <v>63010218</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B224">
+        <v>217</v>
+      </c>
+      <c r="C224">
+        <v>50052</v>
+      </c>
+      <c r="D224">
+        <v>63010219</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B225">
+        <v>218</v>
+      </c>
+      <c r="C225">
+        <v>50052</v>
+      </c>
+      <c r="D225">
+        <v>63010220</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B226">
+        <v>219</v>
+      </c>
+      <c r="C226">
+        <v>50053</v>
+      </c>
+      <c r="D226">
+        <v>63010221</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B227">
+        <v>220</v>
+      </c>
+      <c r="C227">
+        <v>50053</v>
+      </c>
+      <c r="D227">
+        <v>63010222</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B228">
+        <v>221</v>
+      </c>
+      <c r="C228">
+        <v>50054</v>
+      </c>
+      <c r="D228">
+        <v>63010223</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B229">
+        <v>222</v>
+      </c>
+      <c r="C229">
+        <v>50054</v>
+      </c>
+      <c r="D229">
+        <v>63010224</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B230">
+        <v>223</v>
+      </c>
+      <c r="C230">
+        <v>50062</v>
+      </c>
+      <c r="D230">
+        <v>63010225</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B231">
+        <v>224</v>
+      </c>
+      <c r="C231">
+        <v>50062</v>
+      </c>
+      <c r="D231">
+        <v>63010226</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B232">
+        <v>225</v>
+      </c>
+      <c r="C232">
+        <v>50066</v>
+      </c>
+      <c r="D232">
+        <v>63010227</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B233">
+        <v>226</v>
+      </c>
+      <c r="C233">
+        <v>50066</v>
+      </c>
+      <c r="D233">
+        <v>63010228</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B234">
+        <v>227</v>
+      </c>
+      <c r="C234">
+        <v>50067</v>
+      </c>
+      <c r="D234">
+        <v>63010229</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B235">
+        <v>228</v>
+      </c>
+      <c r="C235">
+        <v>50067</v>
+      </c>
+      <c r="D235">
+        <v>63010230</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B236">
+        <v>229</v>
+      </c>
+      <c r="C236">
+        <v>50068</v>
+      </c>
+      <c r="D236">
+        <v>63010231</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B237">
+        <v>230</v>
+      </c>
+      <c r="C237">
+        <v>50068</v>
+      </c>
+      <c r="D237">
+        <v>63010232</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B238">
+        <v>231</v>
+      </c>
+      <c r="C238">
+        <v>50069</v>
+      </c>
+      <c r="D238">
+        <v>63010233</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B239">
+        <v>232</v>
+      </c>
+      <c r="C239">
+        <v>50069</v>
+      </c>
+      <c r="D239">
+        <v>63010234</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B240">
+        <v>233</v>
+      </c>
+      <c r="C240">
+        <v>50070</v>
+      </c>
+      <c r="D240">
+        <v>63010235</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B241">
+        <v>234</v>
+      </c>
+      <c r="C241">
+        <v>50070</v>
+      </c>
+      <c r="D241">
+        <v>63010236</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B242">
+        <v>235</v>
+      </c>
+      <c r="C242">
+        <v>50071</v>
+      </c>
+      <c r="D242">
+        <v>63010237</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B243">
+        <v>236</v>
+      </c>
+      <c r="C243">
+        <v>50071</v>
+      </c>
+      <c r="D243">
+        <v>63010238</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B244">
+        <v>237</v>
+      </c>
+      <c r="C244">
+        <v>50085</v>
+      </c>
+      <c r="D244">
+        <v>63010239</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B245">
+        <v>238</v>
+      </c>
+      <c r="C245">
+        <v>50085</v>
+      </c>
+      <c r="D245">
+        <v>63010240</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B246">
+        <v>239</v>
+      </c>
+      <c r="C246">
+        <v>50087</v>
+      </c>
+      <c r="D246">
+        <v>63010241</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B247">
+        <v>240</v>
+      </c>
+      <c r="C247">
+        <v>50087</v>
+      </c>
+      <c r="D247">
+        <v>63010242</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B248">
+        <v>241</v>
+      </c>
+      <c r="C248">
+        <v>50088</v>
+      </c>
+      <c r="D248">
+        <v>63010243</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B249">
+        <v>242</v>
+      </c>
+      <c r="C249">
+        <v>50088</v>
+      </c>
+      <c r="D249">
+        <v>63010244</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B250">
+        <v>243</v>
+      </c>
+      <c r="C250">
+        <v>50089</v>
+      </c>
+      <c r="D250">
+        <v>63010245</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B251">
+        <v>244</v>
+      </c>
+      <c r="C251">
+        <v>50089</v>
+      </c>
+      <c r="D251">
+        <v>63010246</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B252">
+        <v>245</v>
+      </c>
+      <c r="C252">
+        <v>50090</v>
+      </c>
+      <c r="D252">
+        <v>63010247</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B253">
+        <v>246</v>
+      </c>
+      <c r="C253">
+        <v>50090</v>
+      </c>
+      <c r="D253">
+        <v>63010248</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B254">
+        <v>247</v>
+      </c>
+      <c r="C254">
+        <v>9998</v>
+      </c>
+      <c r="D254">
+        <v>63010249</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B255">
+        <v>248</v>
+      </c>
+      <c r="C255">
+        <v>9998</v>
+      </c>
+      <c r="D255">
+        <v>63010250</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B256">
+        <v>249</v>
+      </c>
+      <c r="C256">
+        <v>9998</v>
+      </c>
+      <c r="D256">
+        <v>63010251</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B257">
+        <v>250</v>
+      </c>
+      <c r="C257">
+        <v>9998</v>
+      </c>
+      <c r="D257">
+        <v>63010252</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B258">
+        <v>251</v>
+      </c>
+      <c r="C258">
+        <v>9998</v>
+      </c>
+      <c r="D258">
+        <v>63010253</v>
+      </c>
+    </row>
+    <row r="259" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B259">
+        <v>252</v>
+      </c>
+      <c r="C259">
+        <v>9998</v>
+      </c>
+      <c r="D259">
+        <v>63010254</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B260">
+        <v>253</v>
+      </c>
+      <c r="C260">
+        <v>9998</v>
+      </c>
+      <c r="D260">
+        <v>63010255</v>
+      </c>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B261">
+        <v>254</v>
+      </c>
+      <c r="C261">
+        <v>9998</v>
+      </c>
+      <c r="D261">
+        <v>63010256</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
